--- a/04_Modules/04_Associate/c_data/04_associate.xlsx
+++ b/04_Modules/04_Associate/c_data/04_associate.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7782" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7843" uniqueCount="350">
   <si>
     <t>sheet</t>
   </si>
@@ -79,7 +79,7 @@
     <t>interaction</t>
   </si>
   <si>
-    <t>Interaction, feature ~ growth x strength gain: effect, t, p, BH, Storey q and the leave-one-out maximum p, per module, window and strength test.</t>
+    <t>Interaction, feature ~ growth x strength gain: effect, t, p, BH, Storey q, the leave-one-out maximum p and the person left out to give it, per module, window and test.</t>
   </si>
   <si>
     <t>flips</t>
@@ -389,6 +389,48 @@
   </si>
   <si>
     <t>strength</t>
+  </si>
+  <si>
+    <t>loo_worst_subject</t>
+  </si>
+  <si>
+    <t>HR_S16</t>
+  </si>
+  <si>
+    <t>LR_S17</t>
+  </si>
+  <si>
+    <t>LR_S21</t>
+  </si>
+  <si>
+    <t>HR_S24</t>
+  </si>
+  <si>
+    <t>HR_S10</t>
+  </si>
+  <si>
+    <t>LR_S04</t>
+  </si>
+  <si>
+    <t>LR_S30</t>
+  </si>
+  <si>
+    <t>HR_S27</t>
+  </si>
+  <si>
+    <t>HR_S22</t>
+  </si>
+  <si>
+    <t>HR_S28</t>
+  </si>
+  <si>
+    <t>HR_S03</t>
+  </si>
+  <si>
+    <t>LR_S06</t>
+  </si>
+  <si>
+    <t>LR_S05</t>
   </si>
   <si>
     <t>hr_rho</t>
@@ -1507,19 +1549,19 @@
         <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>76</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>77</v>
@@ -1554,7 +1596,7 @@
         <v>0.1139430284857571</v>
       </c>
       <c r="I2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J2">
         <v>0.9155422288855573</v>
@@ -1589,7 +1631,7 @@
         <v>0.1974012993503248</v>
       </c>
       <c r="I3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J3">
         <v>0.9155422288855573</v>
@@ -1624,7 +1666,7 @@
         <v>0.3128435782108945</v>
       </c>
       <c r="I4" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J4">
         <v>0.9155422288855573</v>
@@ -1659,7 +1701,7 @@
         <v>0.464767616191904</v>
       </c>
       <c r="I5" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J5">
         <v>0.9155422288855573</v>
@@ -1694,7 +1736,7 @@
         <v>0.5112443778110944</v>
       </c>
       <c r="I6" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J6">
         <v>0.9155422288855573</v>
@@ -1729,7 +1771,7 @@
         <v>0.7066466766616691</v>
       </c>
       <c r="I7" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J7">
         <v>0.9155422288855573</v>
@@ -1764,7 +1806,7 @@
         <v>0.8010994502748626</v>
       </c>
       <c r="I8" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J8">
         <v>0.9155422288855573</v>
@@ -1799,7 +1841,7 @@
         <v>0.8680659670164917</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J9">
         <v>0.9155422288855573</v>
@@ -1834,7 +1876,7 @@
         <v>0.8815592203898051</v>
       </c>
       <c r="I10" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J10">
         <v>0.9155422288855573</v>
@@ -1869,7 +1911,7 @@
         <v>0.9155422288855573</v>
       </c>
       <c r="I11" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J11">
         <v>0.9155422288855573</v>
@@ -1904,7 +1946,7 @@
         <v>0.1589205397301349</v>
       </c>
       <c r="I12" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J12">
         <v>0.7929368649008829</v>
@@ -1939,7 +1981,7 @@
         <v>0.2043978010994503</v>
       </c>
       <c r="I13" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J13">
         <v>0.7929368649008829</v>
@@ -1974,7 +2016,7 @@
         <v>0.2378810594702649</v>
       </c>
       <c r="I14" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J14">
         <v>0.7929368649008829</v>
@@ -2009,7 +2051,7 @@
         <v>0.4607696151924038</v>
       </c>
       <c r="I15" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J15">
         <v>0.9215392303848076</v>
@@ -2044,7 +2086,7 @@
         <v>0.4607696151924038</v>
       </c>
       <c r="I16" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J16">
         <v>0.9215392303848076</v>
@@ -2079,7 +2121,7 @@
         <v>0.696151924037981</v>
       </c>
       <c r="I17" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J17">
         <v>0.975512243878061</v>
@@ -2114,7 +2156,7 @@
         <v>0.7751124437781109</v>
       </c>
       <c r="I18" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J18">
         <v>0.975512243878061</v>
@@ -2149,7 +2191,7 @@
         <v>0.8320839580209896</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J19">
         <v>0.975512243878061</v>
@@ -2184,7 +2226,7 @@
         <v>0.9220389805097451</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J20">
         <v>0.975512243878061</v>
@@ -2219,7 +2261,7 @@
         <v>0.975512243878061</v>
       </c>
       <c r="I21" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J21">
         <v>0.975512243878061</v>
@@ -2254,7 +2296,7 @@
         <v>0.15992003998001</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J22">
         <v>0.9965017491254373</v>
@@ -2289,7 +2331,7 @@
         <v>0.4217891054472764</v>
       </c>
       <c r="I23" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J23">
         <v>0.9965017491254373</v>
@@ -2324,7 +2366,7 @@
         <v>0.519240379810095</v>
       </c>
       <c r="I24" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J24">
         <v>0.9965017491254373</v>
@@ -2359,7 +2401,7 @@
         <v>0.5282358820589705</v>
       </c>
       <c r="I25" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J25">
         <v>0.9965017491254373</v>
@@ -2394,7 +2436,7 @@
         <v>0.5637181409295352</v>
       </c>
       <c r="I26" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J26">
         <v>0.9965017491254373</v>
@@ -2429,7 +2471,7 @@
         <v>0.6921539230384808</v>
       </c>
       <c r="I27" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J27">
         <v>0.9965017491254373</v>
@@ -2464,7 +2506,7 @@
         <v>0.8645677161419291</v>
       </c>
       <c r="I28" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J28">
         <v>0.9965017491254373</v>
@@ -2499,7 +2541,7 @@
         <v>0.9575212393803099</v>
       </c>
       <c r="I29" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J29">
         <v>0.9965017491254373</v>
@@ -2534,7 +2576,7 @@
         <v>0.9965017491254373</v>
       </c>
       <c r="I30" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J30">
         <v>0.9965017491254373</v>
@@ -2569,7 +2611,7 @@
         <v>0.9965017491254373</v>
       </c>
       <c r="I31" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J31">
         <v>0.9965017491254373</v>
@@ -2604,7 +2646,7 @@
         <v>0.1189405297351324</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J32">
         <v>0.9426536731634183</v>
@@ -2639,7 +2681,7 @@
         <v>0.2688655672163918</v>
       </c>
       <c r="I33" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J33">
         <v>0.9426536731634183</v>
@@ -2674,7 +2716,7 @@
         <v>0.3798100949525237</v>
       </c>
       <c r="I34" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J34">
         <v>0.9426536731634183</v>
@@ -2709,7 +2751,7 @@
         <v>0.6296851574212894</v>
       </c>
       <c r="I35" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J35">
         <v>0.9426536731634183</v>
@@ -2744,7 +2786,7 @@
         <v>0.6726636681659171</v>
       </c>
       <c r="I36" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J36">
         <v>0.9426536731634183</v>
@@ -2779,7 +2821,7 @@
         <v>0.7401299350324838</v>
       </c>
       <c r="I37" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J37">
         <v>0.9426536731634183</v>
@@ -2814,7 +2856,7 @@
         <v>0.744127936031984</v>
       </c>
       <c r="I38" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J38">
         <v>0.9426536731634183</v>
@@ -2849,7 +2891,7 @@
         <v>0.7541229385307346</v>
       </c>
       <c r="I39" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J39">
         <v>0.9426536731634183</v>
@@ -2884,7 +2926,7 @@
         <v>0.9225387306346826</v>
       </c>
       <c r="I40" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J40">
         <v>0.9525237381309345</v>
@@ -2919,7 +2961,7 @@
         <v>0.9525237381309345</v>
       </c>
       <c r="I41" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J41">
         <v>0.9525237381309345</v>
@@ -2954,7 +2996,7 @@
         <v>0.01549225387306347</v>
       </c>
       <c r="I42" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J42">
         <v>0.1549225387306347</v>
@@ -2989,7 +3031,7 @@
         <v>0.256871564217891</v>
       </c>
       <c r="I43" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J43">
         <v>0.7321339330334832</v>
@@ -3024,7 +3066,7 @@
         <v>0.3833083458270864</v>
       </c>
       <c r="I44" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J44">
         <v>0.7321339330334832</v>
@@ -3059,7 +3101,7 @@
         <v>0.4167916041979011</v>
       </c>
       <c r="I45" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J45">
         <v>0.7321339330334832</v>
@@ -3094,7 +3136,7 @@
         <v>0.4627686156921539</v>
       </c>
       <c r="I46" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J46">
         <v>0.7321339330334832</v>
@@ -3129,7 +3171,7 @@
         <v>0.4792603698150925</v>
       </c>
       <c r="I47" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J47">
         <v>0.7321339330334832</v>
@@ -3164,7 +3206,7 @@
         <v>0.5747126436781609</v>
       </c>
       <c r="I48" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J48">
         <v>0.7321339330334832</v>
@@ -3199,7 +3241,7 @@
         <v>0.5857071464267866</v>
       </c>
       <c r="I49" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J49">
         <v>0.7321339330334832</v>
@@ -3234,7 +3276,7 @@
         <v>0.7211394302848576</v>
       </c>
       <c r="I50" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J50">
         <v>0.8012660336498418</v>
@@ -3269,7 +3311,7 @@
         <v>0.8735632183908046</v>
       </c>
       <c r="I51" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J51">
         <v>0.8735632183908046</v>
@@ -3304,7 +3346,7 @@
         <v>0.3833083458270864</v>
       </c>
       <c r="I52" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J52">
         <v>0.9780109945027486</v>
@@ -3339,7 +3381,7 @@
         <v>0.4337831084457771</v>
       </c>
       <c r="I53" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J53">
         <v>0.9780109945027486</v>
@@ -3374,7 +3416,7 @@
         <v>0.4912543728135932</v>
       </c>
       <c r="I54" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J54">
         <v>0.9780109945027486</v>
@@ -3409,7 +3451,7 @@
         <v>0.7986006996501749</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J55">
         <v>0.9780109945027486</v>
@@ -3444,7 +3486,7 @@
         <v>0.8585707146426786</v>
       </c>
       <c r="I56" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J56">
         <v>0.9780109945027486</v>
@@ -3479,7 +3521,7 @@
         <v>0.8590704647676162</v>
       </c>
       <c r="I57" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J57">
         <v>0.9780109945027486</v>
@@ -3514,7 +3556,7 @@
         <v>0.8620689655172413</v>
       </c>
       <c r="I58" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J58">
         <v>0.9780109945027486</v>
@@ -3549,7 +3591,7 @@
         <v>0.8940529735132434</v>
       </c>
       <c r="I59" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J59">
         <v>0.9780109945027486</v>
@@ -3584,7 +3626,7 @@
         <v>0.9320339830084957</v>
       </c>
       <c r="I60" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J60">
         <v>0.9780109945027486</v>
@@ -3619,7 +3661,7 @@
         <v>0.9780109945027486</v>
       </c>
       <c r="I61" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J61">
         <v>0.9780109945027486</v>
@@ -3654,7 +3696,7 @@
         <v>0.03448275862068965</v>
       </c>
       <c r="I62" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J62">
         <v>0.3448275862068966</v>
@@ -3689,7 +3731,7 @@
         <v>0.152423788105947</v>
       </c>
       <c r="I63" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J63">
         <v>0.6936531734132934</v>
@@ -3724,7 +3766,7 @@
         <v>0.287856071964018</v>
       </c>
       <c r="I64" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J64">
         <v>0.6936531734132934</v>
@@ -3759,7 +3801,7 @@
         <v>0.4662668665667166</v>
       </c>
       <c r="I65" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J65">
         <v>0.6936531734132934</v>
@@ -3794,7 +3836,7 @@
         <v>0.487256371814093</v>
       </c>
       <c r="I66" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J66">
         <v>0.6936531734132934</v>
@@ -3829,7 +3871,7 @@
         <v>0.5172413793103449</v>
       </c>
       <c r="I67" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J67">
         <v>0.6936531734132934</v>
@@ -3864,7 +3906,7 @@
         <v>0.5467266366816592</v>
       </c>
       <c r="I68" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J68">
         <v>0.6936531734132934</v>
@@ -3899,7 +3941,7 @@
         <v>0.6461769115442278</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J69">
         <v>0.6936531734132934</v>
@@ -3934,7 +3976,7 @@
         <v>0.6776611694152923</v>
       </c>
       <c r="I70" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J70">
         <v>0.6936531734132934</v>
@@ -3969,7 +4011,7 @@
         <v>0.6936531734132934</v>
       </c>
       <c r="I71" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J71">
         <v>0.6936531734132934</v>
@@ -4004,7 +4046,7 @@
         <v>0.2048975512243878</v>
       </c>
       <c r="I72" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J72">
         <v>0.8787273030151592</v>
@@ -4039,7 +4081,7 @@
         <v>0.3973013493253373</v>
       </c>
       <c r="I73" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J73">
         <v>0.8787273030151592</v>
@@ -4074,7 +4116,7 @@
         <v>0.4182908545727136</v>
       </c>
       <c r="I74" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J74">
         <v>0.8787273030151592</v>
@@ -4109,7 +4151,7 @@
         <v>0.4617691154422789</v>
       </c>
       <c r="I75" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J75">
         <v>0.8787273030151592</v>
@@ -4144,7 +4186,7 @@
         <v>0.5047476261869065</v>
       </c>
       <c r="I76" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J76">
         <v>0.8787273030151592</v>
@@ -4179,7 +4221,7 @@
         <v>0.5272363818090955</v>
       </c>
       <c r="I77" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J77">
         <v>0.8787273030151592</v>
@@ -4214,7 +4256,7 @@
         <v>0.7221389305347327</v>
       </c>
       <c r="I78" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J78">
         <v>0.8820589705147426</v>
@@ -4249,7 +4291,7 @@
         <v>0.824087956021989</v>
       </c>
       <c r="I79" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J79">
         <v>0.8820589705147426</v>
@@ -4284,7 +4326,7 @@
         <v>0.872063968015992</v>
       </c>
       <c r="I80" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J80">
         <v>0.8820589705147426</v>
@@ -4319,7 +4361,7 @@
         <v>0.8820589705147426</v>
       </c>
       <c r="I81" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J81">
         <v>0.8820589705147426</v>
@@ -4354,7 +4396,7 @@
         <v>0.05197401299350324</v>
       </c>
       <c r="I82" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J82">
         <v>0.5197401299350325</v>
@@ -4389,7 +4431,7 @@
         <v>0.1099450274862569</v>
       </c>
       <c r="I83" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J83">
         <v>0.5497251374312844</v>
@@ -4424,7 +4466,7 @@
         <v>0.6006996501749126</v>
       </c>
       <c r="I84" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J84">
         <v>0.9635182408795602</v>
@@ -4459,7 +4501,7 @@
         <v>0.6116941529235382</v>
       </c>
       <c r="I85" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J85">
         <v>0.9635182408795602</v>
@@ -4494,7 +4536,7 @@
         <v>0.7286356821589205</v>
       </c>
       <c r="I86" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J86">
         <v>0.9635182408795602</v>
@@ -4529,7 +4571,7 @@
         <v>0.7346326836581709</v>
       </c>
       <c r="I87" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J87">
         <v>0.9635182408795602</v>
@@ -4564,7 +4606,7 @@
         <v>0.9185407296351824</v>
       </c>
       <c r="I88" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J88">
         <v>0.9635182408795602</v>
@@ -4599,7 +4641,7 @@
         <v>0.9465267366316842</v>
       </c>
       <c r="I89" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J89">
         <v>0.9635182408795602</v>
@@ -4634,7 +4676,7 @@
         <v>0.9635182408795602</v>
       </c>
       <c r="I90" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J90">
         <v>0.9635182408795602</v>
@@ -4669,7 +4711,7 @@
         <v>0.9635182408795602</v>
       </c>
       <c r="I91" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J91">
         <v>0.9635182408795602</v>
@@ -4704,7 +4746,7 @@
         <v>0.2218890554722639</v>
       </c>
       <c r="I92" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J92">
         <v>0.7021489255372314</v>
@@ -4739,7 +4781,7 @@
         <v>0.223888055972014</v>
       </c>
       <c r="I93" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J93">
         <v>0.7021489255372314</v>
@@ -4774,7 +4816,7 @@
         <v>0.3238380809595202</v>
       </c>
       <c r="I94" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J94">
         <v>0.7021489255372314</v>
@@ -4809,7 +4851,7 @@
         <v>0.3383308345827086</v>
       </c>
       <c r="I95" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J95">
         <v>0.7021489255372314</v>
@@ -4844,7 +4886,7 @@
         <v>0.3513243378310845</v>
       </c>
       <c r="I96" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J96">
         <v>0.7021489255372314</v>
@@ -4879,7 +4921,7 @@
         <v>0.4212893553223389</v>
       </c>
       <c r="I97" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J97">
         <v>0.7021489255372314</v>
@@ -4914,7 +4956,7 @@
         <v>0.7691154422788605</v>
       </c>
       <c r="I98" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J98">
         <v>0.8870564717641179</v>
@@ -4949,7 +4991,7 @@
         <v>0.7691154422788605</v>
       </c>
       <c r="I99" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J99">
         <v>0.8870564717641179</v>
@@ -4984,7 +5026,7 @@
         <v>0.84007996001999</v>
       </c>
       <c r="I100" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J100">
         <v>0.8870564717641179</v>
@@ -5019,7 +5061,7 @@
         <v>0.8870564717641179</v>
       </c>
       <c r="I101" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J101">
         <v>0.8870564717641179</v>
@@ -5054,7 +5096,7 @@
         <v>0.01649175412293853</v>
       </c>
       <c r="I102" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J102">
         <v>0.1649175412293853</v>
@@ -5089,7 +5131,7 @@
         <v>0.09695152423788106</v>
       </c>
       <c r="I103" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J103">
         <v>0.4847576211894053</v>
@@ -5124,7 +5166,7 @@
         <v>0.2123938030984508</v>
       </c>
       <c r="I104" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J104">
         <v>0.5809595202398801</v>
@@ -5159,7 +5201,7 @@
         <v>0.232383808095952</v>
       </c>
       <c r="I105" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J105">
         <v>0.5809595202398801</v>
@@ -5194,7 +5236,7 @@
         <v>0.2958520739630185</v>
       </c>
       <c r="I106" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J106">
         <v>0.591704147926037</v>
@@ -5229,7 +5271,7 @@
         <v>0.5802098950524738</v>
       </c>
       <c r="I107" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J107">
         <v>0.8708145927036481</v>
@@ -5264,7 +5306,7 @@
         <v>0.6131934032983508</v>
       </c>
       <c r="I108" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J108">
         <v>0.8708145927036481</v>
@@ -5299,7 +5341,7 @@
         <v>0.6966516741629185</v>
       </c>
       <c r="I109" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J109">
         <v>0.8708145927036481</v>
@@ -5334,7 +5376,7 @@
         <v>0.863568215892054</v>
       </c>
       <c r="I110" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J110">
         <v>0.9105447276361819</v>
@@ -5369,7 +5411,7 @@
         <v>0.9105447276361819</v>
       </c>
       <c r="I111" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J111">
         <v>0.9105447276361819</v>
@@ -5404,7 +5446,7 @@
         <v>0.01849075462268866</v>
       </c>
       <c r="I112" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J112">
         <v>0.1849075462268865</v>
@@ -5439,7 +5481,7 @@
         <v>0.06896551724137931</v>
       </c>
       <c r="I113" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J113">
         <v>0.2798600699650175</v>
@@ -5474,7 +5516,7 @@
         <v>0.08395802098950525</v>
       </c>
       <c r="I114" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J114">
         <v>0.2798600699650175</v>
@@ -5509,7 +5551,7 @@
         <v>0.1409295352323838</v>
       </c>
       <c r="I115" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J115">
         <v>0.3523238380809595</v>
@@ -5544,7 +5586,7 @@
         <v>0.2743628185907047</v>
       </c>
       <c r="I116" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J116">
         <v>0.5055805430618024</v>
@@ -5579,7 +5621,7 @@
         <v>0.3033483258370814</v>
       </c>
       <c r="I117" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J117">
         <v>0.5055805430618024</v>
@@ -5614,7 +5656,7 @@
         <v>0.4387806096951524</v>
       </c>
       <c r="I118" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J118">
         <v>0.6268294424216463</v>
@@ -5649,7 +5691,7 @@
         <v>0.6251874062968515</v>
       </c>
       <c r="I119" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J119">
         <v>0.7814842578710645</v>
@@ -5684,7 +5726,7 @@
         <v>0.7531234382808596</v>
       </c>
       <c r="I120" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J120">
         <v>0.8368038203120662</v>
@@ -5719,7 +5761,7 @@
         <v>0.9900049975012494</v>
       </c>
       <c r="I121" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J121">
         <v>0.9900049975012494</v>
@@ -5754,7 +5796,7 @@
         <v>0.009995002498750625</v>
       </c>
       <c r="I122" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J122">
         <v>0.09995002498750626</v>
@@ -5789,7 +5831,7 @@
         <v>0.2463768115942029</v>
       </c>
       <c r="I123" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J123">
         <v>0.7536231884057971</v>
@@ -5824,7 +5866,7 @@
         <v>0.2938530734632684</v>
       </c>
       <c r="I124" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J124">
         <v>0.7536231884057971</v>
@@ -5859,7 +5901,7 @@
         <v>0.3593203398300849</v>
       </c>
       <c r="I125" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J125">
         <v>0.7536231884057971</v>
@@ -5894,7 +5936,7 @@
         <v>0.3768115942028986</v>
       </c>
       <c r="I126" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J126">
         <v>0.7536231884057971</v>
@@ -5929,7 +5971,7 @@
         <v>0.5312343828085957</v>
       </c>
       <c r="I127" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J127">
         <v>0.8202148925537232</v>
@@ -5964,7 +6006,7 @@
         <v>0.6071964017991005</v>
       </c>
       <c r="I128" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J128">
         <v>0.8202148925537232</v>
@@ -5999,7 +6041,7 @@
         <v>0.6561719140429785</v>
       </c>
       <c r="I129" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J129">
         <v>0.8202148925537232</v>
@@ -6034,7 +6076,7 @@
         <v>0.8745627186406797</v>
       </c>
       <c r="I130" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J130">
         <v>0.9055472263868066</v>
@@ -6069,7 +6111,7 @@
         <v>0.9055472263868066</v>
       </c>
       <c r="I131" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J131">
         <v>0.9055472263868066</v>
@@ -6104,7 +6146,7 @@
         <v>0.003498250874562719</v>
       </c>
       <c r="I132" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J132">
         <v>0.03498250874562719</v>
@@ -6139,7 +6181,7 @@
         <v>0.031984007996002</v>
       </c>
       <c r="I133" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J133">
         <v>0.15992003998001</v>
@@ -6174,7 +6216,7 @@
         <v>0.06096951524237881</v>
       </c>
       <c r="I134" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J134">
         <v>0.2032317174745961</v>
@@ -6209,7 +6251,7 @@
         <v>0.183408295852074</v>
       </c>
       <c r="I135" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J135">
         <v>0.3389971680826254</v>
@@ -6244,7 +6286,7 @@
         <v>0.1884057971014493</v>
       </c>
       <c r="I136" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J136">
         <v>0.3389971680826254</v>
@@ -6279,7 +6321,7 @@
         <v>0.2033983008495752</v>
       </c>
       <c r="I137" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J137">
         <v>0.3389971680826254</v>
@@ -6314,7 +6356,7 @@
         <v>0.2758620689655172</v>
       </c>
       <c r="I138" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J138">
         <v>0.3940886699507389</v>
@@ -6349,7 +6391,7 @@
         <v>0.4532733633183408</v>
       </c>
       <c r="I139" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J139">
         <v>0.566591704147926</v>
@@ -6384,7 +6426,7 @@
         <v>0.7251374312843578</v>
       </c>
       <c r="I140" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J140">
         <v>0.7766116941529235</v>
@@ -6419,7 +6461,7 @@
         <v>0.7766116941529235</v>
       </c>
       <c r="I141" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J141">
         <v>0.7766116941529235</v>
@@ -6454,7 +6496,7 @@
         <v>0.1179410294852574</v>
       </c>
       <c r="I142" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J142">
         <v>0.6066966516741629</v>
@@ -6489,7 +6531,7 @@
         <v>0.1404297851074463</v>
       </c>
       <c r="I143" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J143">
         <v>0.6066966516741629</v>
@@ -6524,7 +6566,7 @@
         <v>0.2553723138430785</v>
       </c>
       <c r="I144" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J144">
         <v>0.6066966516741629</v>
@@ -6559,7 +6601,7 @@
         <v>0.2658670664667666</v>
       </c>
       <c r="I145" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J145">
         <v>0.6066966516741629</v>
@@ -6594,7 +6636,7 @@
         <v>0.3033483258370814</v>
       </c>
       <c r="I146" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J146">
         <v>0.6066966516741629</v>
@@ -6629,7 +6671,7 @@
         <v>0.4517741129435283</v>
       </c>
       <c r="I147" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J147">
         <v>0.7529568549058805</v>
@@ -6664,7 +6706,7 @@
         <v>0.6196901549225388</v>
       </c>
       <c r="I148" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J148">
         <v>0.8095952023988006</v>
@@ -6699,7 +6741,7 @@
         <v>0.7026486756621689</v>
       </c>
       <c r="I149" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J149">
         <v>0.8095952023988006</v>
@@ -6734,7 +6776,7 @@
         <v>0.7286356821589205</v>
       </c>
       <c r="I150" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J150">
         <v>0.8095952023988006</v>
@@ -6769,7 +6811,7 @@
         <v>0.847576211894053</v>
       </c>
       <c r="I151" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J151">
         <v>0.847576211894053</v>
@@ -6804,7 +6846,7 @@
         <v>0.001499250374812594</v>
       </c>
       <c r="I152" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J152">
         <v>0.01499250374812594</v>
@@ -6839,7 +6881,7 @@
         <v>0.01449275362318841</v>
       </c>
       <c r="I153" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J153">
         <v>0.07246376811594203</v>
@@ -6874,7 +6916,7 @@
         <v>0.02448775612193903</v>
       </c>
       <c r="I154" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J154">
         <v>0.08162585373979678</v>
@@ -6909,7 +6951,7 @@
         <v>0.1314342828585707</v>
       </c>
       <c r="I155" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J155">
         <v>0.3108445777111444</v>
@@ -6944,7 +6986,7 @@
         <v>0.1554222888555722</v>
       </c>
       <c r="I156" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J156">
         <v>0.3108445777111444</v>
@@ -6979,7 +7021,7 @@
         <v>0.3353323338330835</v>
       </c>
       <c r="I157" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J157">
         <v>0.5588872230551392</v>
@@ -7014,7 +7056,7 @@
         <v>0.6596701649175413</v>
       </c>
       <c r="I158" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J158">
         <v>0.84007996001999</v>
@@ -7049,7 +7091,7 @@
         <v>0.6831584207896052</v>
       </c>
       <c r="I159" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J159">
         <v>0.84007996001999</v>
@@ -7084,7 +7126,7 @@
         <v>0.7566216891554223</v>
       </c>
       <c r="I160" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J160">
         <v>0.84007996001999</v>
@@ -7119,7 +7161,7 @@
         <v>0.84007996001999</v>
       </c>
       <c r="I161" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J161">
         <v>0.84007996001999</v>
@@ -7154,7 +7196,7 @@
         <v>0.06496751624187906</v>
       </c>
       <c r="I162" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J162">
         <v>0.6496751624187906</v>
@@ -7189,7 +7231,7 @@
         <v>0.136431784107946</v>
       </c>
       <c r="I163" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J163">
         <v>0.671664167916042</v>
@@ -7224,7 +7266,7 @@
         <v>0.2648675662168916</v>
       </c>
       <c r="I164" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J164">
         <v>0.671664167916042</v>
@@ -7259,7 +7301,7 @@
         <v>0.3608195902048976</v>
       </c>
       <c r="I165" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J165">
         <v>0.671664167916042</v>
@@ -7294,7 +7336,7 @@
         <v>0.4282858570714643</v>
       </c>
       <c r="I166" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J166">
         <v>0.671664167916042</v>
@@ -7329,7 +7371,7 @@
         <v>0.4287856071964018</v>
       </c>
       <c r="I167" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J167">
         <v>0.671664167916042</v>
@@ -7364,7 +7406,7 @@
         <v>0.5592203898050975</v>
       </c>
       <c r="I168" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J168">
         <v>0.671664167916042</v>
@@ -7399,7 +7441,7 @@
         <v>0.6156921539230384</v>
       </c>
       <c r="I169" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J169">
         <v>0.671664167916042</v>
@@ -7434,7 +7476,7 @@
         <v>0.6261869065467266</v>
       </c>
       <c r="I170" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J170">
         <v>0.671664167916042</v>
@@ -7469,7 +7511,7 @@
         <v>0.671664167916042</v>
       </c>
       <c r="I171" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J171">
         <v>0.671664167916042</v>
@@ -7504,7 +7546,7 @@
         <v>0.047976011994003</v>
       </c>
       <c r="I172" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J172">
         <v>0.2931867399633517</v>
@@ -7539,7 +7581,7 @@
         <v>0.06896551724137931</v>
       </c>
       <c r="I173" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J173">
         <v>0.2931867399633517</v>
@@ -7574,7 +7616,7 @@
         <v>0.0879560219890055</v>
       </c>
       <c r="I174" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J174">
         <v>0.2931867399633517</v>
@@ -7609,7 +7651,7 @@
         <v>0.1429285357321339</v>
       </c>
       <c r="I175" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J175">
         <v>0.3573213393303348</v>
@@ -7644,7 +7686,7 @@
         <v>0.3383308345827086</v>
       </c>
       <c r="I176" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J176">
         <v>0.5863734799267033</v>
@@ -7679,7 +7721,7 @@
         <v>0.351824087956022</v>
       </c>
       <c r="I177" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J177">
         <v>0.5863734799267033</v>
@@ -7714,7 +7756,7 @@
         <v>0.4907546226886557</v>
       </c>
       <c r="I178" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J178">
         <v>0.6428035982008995</v>
@@ -7749,7 +7791,7 @@
         <v>0.5142428785607196</v>
       </c>
       <c r="I179" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J179">
         <v>0.6428035982008995</v>
@@ -7784,7 +7826,7 @@
         <v>0.5797101449275363</v>
       </c>
       <c r="I180" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J180">
         <v>0.6441223832528181</v>
@@ -7819,7 +7861,7 @@
         <v>0.8890554722638681</v>
       </c>
       <c r="I181" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J181">
         <v>0.8890554722638681</v>
@@ -7854,7 +7896,7 @@
         <v>0.1239380309845077</v>
       </c>
       <c r="I182" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J182">
         <v>0.7641179410294853</v>
@@ -7889,7 +7931,7 @@
         <v>0.2828585707146427</v>
       </c>
       <c r="I183" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J183">
         <v>0.7641179410294853</v>
@@ -7924,7 +7966,7 @@
         <v>0.3053473263368316</v>
       </c>
       <c r="I184" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J184">
         <v>0.7641179410294853</v>
@@ -7959,7 +8001,7 @@
         <v>0.4022988505747127</v>
       </c>
       <c r="I185" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J185">
         <v>0.7641179410294853</v>
@@ -7994,7 +8036,7 @@
         <v>0.4022988505747127</v>
       </c>
       <c r="I186" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J186">
         <v>0.7641179410294853</v>
@@ -8029,7 +8071,7 @@
         <v>0.5932033983008496</v>
       </c>
       <c r="I187" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J187">
         <v>0.7641179410294853</v>
@@ -8064,7 +8106,7 @@
         <v>0.6041979010494752</v>
       </c>
       <c r="I188" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J188">
         <v>0.7641179410294853</v>
@@ -8099,7 +8141,7 @@
         <v>0.6956521739130435</v>
       </c>
       <c r="I189" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J189">
         <v>0.7641179410294853</v>
@@ -8134,7 +8176,7 @@
         <v>0.7246376811594203</v>
       </c>
       <c r="I190" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J190">
         <v>0.7641179410294853</v>
@@ -8169,7 +8211,7 @@
         <v>0.7641179410294853</v>
       </c>
       <c r="I191" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J191">
         <v>0.7641179410294853</v>
@@ -8204,7 +8246,7 @@
         <v>0.05897051474262868</v>
       </c>
       <c r="I192" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J192">
         <v>0.5897051474262869</v>
@@ -8239,7 +8281,7 @@
         <v>0.2808595702148926</v>
       </c>
       <c r="I193" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J193">
         <v>0.8708145927036481</v>
@@ -8274,7 +8316,7 @@
         <v>0.3313343328335832</v>
       </c>
       <c r="I194" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J194">
         <v>0.8708145927036481</v>
@@ -8309,7 +8351,7 @@
         <v>0.567216391804098</v>
       </c>
       <c r="I195" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J195">
         <v>0.8708145927036481</v>
@@ -8344,7 +8386,7 @@
         <v>0.592703648175912</v>
       </c>
       <c r="I196" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J196">
         <v>0.8708145927036481</v>
@@ -8379,7 +8421,7 @@
         <v>0.6261869065467266</v>
       </c>
       <c r="I197" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J197">
         <v>0.8708145927036481</v>
@@ -8414,7 +8456,7 @@
         <v>0.6306846576711644</v>
       </c>
       <c r="I198" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J198">
         <v>0.8708145927036481</v>
@@ -8449,7 +8491,7 @@
         <v>0.6966516741629185</v>
       </c>
       <c r="I199" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J199">
         <v>0.8708145927036481</v>
@@ -8484,7 +8526,7 @@
         <v>0.9340329835082459</v>
       </c>
       <c r="I200" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J200">
         <v>0.9660169915042479</v>
@@ -8519,7 +8561,7 @@
         <v>0.9660169915042479</v>
       </c>
       <c r="I201" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J201">
         <v>0.9660169915042479</v>
@@ -8554,7 +8596,7 @@
         <v>0.06096951524237881</v>
       </c>
       <c r="I202" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J202">
         <v>0.6096951524237881</v>
@@ -8589,7 +8631,7 @@
         <v>0.1794102948525737</v>
       </c>
       <c r="I203" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J203">
         <v>0.6346826586706648</v>
@@ -8624,7 +8666,7 @@
         <v>0.1904047976011994</v>
       </c>
       <c r="I204" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J204">
         <v>0.6346826586706648</v>
@@ -8659,7 +8701,7 @@
         <v>0.463768115942029</v>
       </c>
       <c r="I205" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J205">
         <v>0.9515242378810594</v>
@@ -8694,7 +8736,7 @@
         <v>0.4962518740629685</v>
       </c>
       <c r="I206" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J206">
         <v>0.9515242378810594</v>
@@ -8729,7 +8771,7 @@
         <v>0.6176911544227887</v>
       </c>
       <c r="I207" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J207">
         <v>0.9515242378810594</v>
@@ -8764,7 +8806,7 @@
         <v>0.6796601699150425</v>
       </c>
       <c r="I208" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J208">
         <v>0.9515242378810594</v>
@@ -8799,7 +8841,7 @@
         <v>0.9435282358820589</v>
       </c>
       <c r="I209" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J209">
         <v>0.9515242378810594</v>
@@ -8834,7 +8876,7 @@
         <v>0.9495252373813093</v>
       </c>
       <c r="I210" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J210">
         <v>0.9515242378810594</v>
@@ -8869,7 +8911,7 @@
         <v>0.9515242378810594</v>
       </c>
       <c r="I211" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J211">
         <v>0.9515242378810594</v>
@@ -8904,7 +8946,7 @@
         <v>0.09095452273863068</v>
       </c>
       <c r="I212" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J212">
         <v>0.9095452273863068</v>
@@ -8939,7 +8981,7 @@
         <v>0.3943028485757121</v>
       </c>
       <c r="I213" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J213">
         <v>0.9120439780109946</v>
@@ -8974,7 +9016,7 @@
         <v>0.5312343828085957</v>
       </c>
       <c r="I214" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J214">
         <v>0.9120439780109946</v>
@@ -9009,7 +9051,7 @@
         <v>0.5867066466766616</v>
       </c>
       <c r="I215" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J215">
         <v>0.9120439780109946</v>
@@ -9044,7 +9086,7 @@
         <v>0.6421789105447276</v>
       </c>
       <c r="I216" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J216">
         <v>0.9120439780109946</v>
@@ -9079,7 +9121,7 @@
         <v>0.6946526736631684</v>
       </c>
       <c r="I217" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J217">
         <v>0.9120439780109946</v>
@@ -9114,7 +9156,7 @@
         <v>0.6946526736631684</v>
       </c>
       <c r="I218" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J218">
         <v>0.9120439780109946</v>
@@ -9149,7 +9191,7 @@
         <v>0.7296351824087957</v>
       </c>
       <c r="I219" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J219">
         <v>0.9120439780109946</v>
@@ -9184,7 +9226,7 @@
         <v>0.8255872063968016</v>
       </c>
       <c r="I220" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J220">
         <v>0.9173191182186685</v>
@@ -9219,7 +9261,7 @@
         <v>0.9195402298850575</v>
       </c>
       <c r="I221" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J221">
         <v>0.9195402298850575</v>
@@ -9254,7 +9296,7 @@
         <v>0.03548225887056472</v>
       </c>
       <c r="I222" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J222">
         <v>0.3548225887056472</v>
@@ -9289,7 +9331,7 @@
         <v>0.1454272863568216</v>
       </c>
       <c r="I223" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J223">
         <v>0.6506746626686657</v>
@@ -9324,7 +9366,7 @@
         <v>0.287856071964018</v>
       </c>
       <c r="I224" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J224">
         <v>0.6506746626686657</v>
@@ -9359,7 +9401,7 @@
         <v>0.2893553223388306</v>
       </c>
       <c r="I225" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J225">
         <v>0.6506746626686657</v>
@@ -9394,7 +9436,7 @@
         <v>0.3253373313343328</v>
       </c>
       <c r="I226" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J226">
         <v>0.6506746626686657</v>
@@ -9429,7 +9471,7 @@
         <v>0.5367316341829086</v>
       </c>
       <c r="I227" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J227">
         <v>0.7981009495252374</v>
@@ -9464,7 +9506,7 @@
         <v>0.6706646676661669</v>
       </c>
       <c r="I228" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J228">
         <v>0.7981009495252374</v>
@@ -9499,7 +9541,7 @@
         <v>0.7801099450274862</v>
       </c>
       <c r="I229" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J229">
         <v>0.7981009495252374</v>
@@ -9534,7 +9576,7 @@
         <v>0.7981009495252374</v>
       </c>
       <c r="I230" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J230">
         <v>0.7981009495252374</v>
@@ -9569,7 +9611,7 @@
         <v>0.7981009495252374</v>
       </c>
       <c r="I231" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J231">
         <v>0.7981009495252374</v>
@@ -9601,7 +9643,7 @@
         <v>0.001499250374812594</v>
       </c>
       <c r="I232" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J232">
         <v>0.01499250374812594</v>
@@ -9636,7 +9678,7 @@
         <v>0.1099450274862569</v>
       </c>
       <c r="I233" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J233">
         <v>0.399800099950025</v>
@@ -9671,7 +9713,7 @@
         <v>0.1199400299850075</v>
       </c>
       <c r="I234" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J234">
         <v>0.399800099950025</v>
@@ -9706,7 +9748,7 @@
         <v>0.223888055972014</v>
       </c>
       <c r="I235" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J235">
         <v>0.559720139930035</v>
@@ -9741,7 +9783,7 @@
         <v>0.2938530734632684</v>
       </c>
       <c r="I236" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J236">
         <v>0.5877061469265368</v>
@@ -9776,7 +9818,7 @@
         <v>0.4482758620689655</v>
       </c>
       <c r="I237" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J237">
         <v>0.7057582319951136</v>
@@ -9811,7 +9853,7 @@
         <v>0.6156921539230384</v>
       </c>
       <c r="I238" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J238">
         <v>0.7057582319951136</v>
@@ -9846,7 +9888,7 @@
         <v>0.6351824087956022</v>
       </c>
       <c r="I239" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J239">
         <v>0.7057582319951136</v>
@@ -9881,7 +9923,7 @@
         <v>0.6351824087956022</v>
       </c>
       <c r="I240" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J240">
         <v>0.7057582319951136</v>
@@ -9916,7 +9958,7 @@
         <v>0.9625187406296851</v>
       </c>
       <c r="I241" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J241">
         <v>0.9625187406296851</v>
@@ -9951,7 +9993,7 @@
         <v>0.05047476261869065</v>
       </c>
       <c r="I242" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J242">
         <v>0.5047476261869065</v>
@@ -9986,7 +10028,7 @@
         <v>0.1409295352323838</v>
       </c>
       <c r="I243" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J243">
         <v>0.6146926536731634</v>
@@ -10021,7 +10063,7 @@
         <v>0.184407796101949</v>
       </c>
       <c r="I244" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J244">
         <v>0.6146926536731634</v>
@@ -10056,7 +10098,7 @@
         <v>0.3183408295852074</v>
       </c>
       <c r="I245" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J245">
         <v>0.7116441779110445</v>
@@ -10091,7 +10133,7 @@
         <v>0.3558220889555223</v>
       </c>
       <c r="I246" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J246">
         <v>0.7116441779110445</v>
@@ -10126,7 +10168,7 @@
         <v>0.4777611194402799</v>
       </c>
       <c r="I247" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J247">
         <v>0.7962685324004665</v>
@@ -10161,7 +10203,7 @@
         <v>0.5847076461769115</v>
       </c>
       <c r="I248" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J248">
         <v>0.8352966373955879</v>
@@ -10196,7 +10238,7 @@
         <v>0.6826586706646677</v>
       </c>
       <c r="I249" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J249">
         <v>0.8533233383308346</v>
@@ -10231,7 +10273,7 @@
         <v>0.8995502248875562</v>
       </c>
       <c r="I250" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J250">
         <v>0.9870064967516242</v>
@@ -10266,7 +10308,7 @@
         <v>0.9870064967516242</v>
       </c>
       <c r="I251" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J251">
         <v>0.9870064967516242</v>
@@ -10301,7 +10343,7 @@
         <v>0.1429285357321339</v>
       </c>
       <c r="I252" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J252">
         <v>0.7829418624021323</v>
@@ -10336,7 +10378,7 @@
         <v>0.2098950524737631</v>
       </c>
       <c r="I253" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J253">
         <v>0.7829418624021323</v>
@@ -10371,7 +10413,7 @@
         <v>0.2348825587206397</v>
       </c>
       <c r="I254" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J254">
         <v>0.7829418624021323</v>
@@ -10406,7 +10448,7 @@
         <v>0.3248375812093953</v>
       </c>
       <c r="I255" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J255">
         <v>0.8120939530234883</v>
@@ -10441,7 +10483,7 @@
         <v>0.7116441779110445</v>
       </c>
       <c r="I256" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J256">
         <v>0.9725137431284357</v>
@@ -10476,7 +10518,7 @@
         <v>0.7326336831584208</v>
       </c>
       <c r="I257" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J257">
         <v>0.9725137431284357</v>
@@ -10511,7 +10553,7 @@
         <v>0.9075462268865567</v>
       </c>
       <c r="I258" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J258">
         <v>0.9725137431284357</v>
@@ -10546,7 +10588,7 @@
         <v>0.9220389805097451</v>
       </c>
       <c r="I259" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J259">
         <v>0.9725137431284357</v>
@@ -10581,7 +10623,7 @@
         <v>0.9695152423788106</v>
       </c>
       <c r="I260" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J260">
         <v>0.9725137431284357</v>
@@ -10616,7 +10658,7 @@
         <v>0.9725137431284357</v>
       </c>
       <c r="I261" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J261">
         <v>0.9725137431284357</v>
@@ -10643,7 +10685,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>69</v>
@@ -10655,7 +10697,7 @@
         <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>91</v>
@@ -10672,10 +10714,10 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -10683,10 +10725,10 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -10694,10 +10736,10 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -10705,10 +10747,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -10716,10 +10758,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -10727,10 +10769,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -10807,7 +10849,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B11" t="s">
         <v>84</v>
@@ -10830,7 +10872,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -10853,7 +10895,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
@@ -10876,7 +10918,7 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B14" t="s">
         <v>87</v>
@@ -10899,7 +10941,7 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
@@ -10922,7 +10964,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
         <v>87</v>
@@ -10945,7 +10987,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
         <v>87</v>
@@ -10968,7 +11010,7 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s">
         <v>89</v>
@@ -10991,7 +11033,7 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
         <v>87</v>
@@ -11014,7 +11056,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
         <v>87</v>
@@ -11037,7 +11079,7 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B21" t="s">
         <v>82</v>
@@ -11060,7 +11102,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B22" t="s">
         <v>86</v>
@@ -11083,7 +11125,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s">
         <v>87</v>
@@ -11106,7 +11148,7 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s">
         <v>84</v>
@@ -11129,7 +11171,7 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
         <v>86</v>
@@ -11152,7 +11194,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
         <v>82</v>
@@ -11175,7 +11217,7 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
         <v>83</v>
@@ -11204,7 +11246,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
         <v>87</v>
@@ -11233,7 +11275,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
         <v>87</v>
@@ -11272,35 +11314,35 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -11315,1014 +11357,1014 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" t="s">
         <v>171</v>
-      </c>
-      <c r="B9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C16" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C21" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C22" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C27" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B28" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="B29" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="B30" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B32" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B33" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C33" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B34" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B37" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C39" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C41" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B43" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="B44" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C44" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="B45" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C45" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C49" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B50" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C50" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="B51" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C52" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B54" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C55" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C56" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C57" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B60" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="B62" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B63" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B66" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B67" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B69" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B70" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B71" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="C71" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="C72" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B73" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B74" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B75" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B76" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B80" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C80" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B81" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C81" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B82" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C82" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C83" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B84" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="C84" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B85" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C85" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B86" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B87" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C87" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B88" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C88" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B89" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C89" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C91" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B92" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -60000,10 +60042,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1">
+    <row r="1" spans="1:12" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
@@ -60032,13 +60074,16 @@
         <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -60066,14 +60111,17 @@
       <c r="I2">
         <v>0.9101729953685892</v>
       </c>
-      <c r="J2">
-        <v>0.6691028457527449</v>
+      <c r="J2" t="s">
+        <v>122</v>
       </c>
       <c r="K2">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -60101,14 +60149,17 @@
       <c r="I3">
         <v>0.4546762032722966</v>
       </c>
-      <c r="J3">
-        <v>0.6691028457527449</v>
+      <c r="J3" t="s">
+        <v>122</v>
       </c>
       <c r="K3">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -60136,14 +60187,17 @@
       <c r="I4">
         <v>0.6292306653074429</v>
       </c>
-      <c r="J4">
-        <v>0.6691028457527449</v>
+      <c r="J4" t="s">
+        <v>123</v>
       </c>
       <c r="K4">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -60171,14 +60225,17 @@
       <c r="I5">
         <v>0.9501277450705066</v>
       </c>
-      <c r="J5">
-        <v>0.6691028457527449</v>
+      <c r="J5" t="s">
+        <v>124</v>
       </c>
       <c r="K5">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -60206,14 +60263,17 @@
       <c r="I6">
         <v>0.9985018375955689</v>
       </c>
-      <c r="J6">
-        <v>0.6691028457527449</v>
+      <c r="J6" t="s">
+        <v>124</v>
       </c>
       <c r="K6">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -60241,14 +60301,17 @@
       <c r="I7">
         <v>0.9961729701266945</v>
       </c>
-      <c r="J7">
-        <v>0.6691028457527449</v>
+      <c r="J7" t="s">
+        <v>123</v>
       </c>
       <c r="K7">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>100</v>
       </c>
@@ -60276,14 +60339,17 @@
       <c r="I8">
         <v>0.969051213524398</v>
       </c>
-      <c r="J8">
-        <v>0.6691028457527449</v>
+      <c r="J8" t="s">
+        <v>122</v>
       </c>
       <c r="K8">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -60311,14 +60377,17 @@
       <c r="I9">
         <v>0.991674609245588</v>
       </c>
-      <c r="J9">
-        <v>0.6691028457527449</v>
+      <c r="J9" t="s">
+        <v>123</v>
       </c>
       <c r="K9">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>100</v>
       </c>
@@ -60346,14 +60415,17 @@
       <c r="I10">
         <v>0.8884602720239705</v>
       </c>
-      <c r="J10">
-        <v>0.6691028457527449</v>
+      <c r="J10" t="s">
+        <v>123</v>
       </c>
       <c r="K10">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -60381,14 +60453,17 @@
       <c r="I11">
         <v>0.7958517504493536</v>
       </c>
-      <c r="J11">
-        <v>0.6691028457527449</v>
+      <c r="J11" t="s">
+        <v>125</v>
       </c>
       <c r="K11">
         <v>0.6691028457527449</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>0.6691028457527449</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -60416,14 +60491,17 @@
       <c r="I12">
         <v>0.3354007583106147</v>
       </c>
-      <c r="J12">
-        <v>0.4598284394497052</v>
+      <c r="J12" t="s">
+        <v>126</v>
       </c>
       <c r="K12">
         <v>0.4598284394497052</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>0.4598284394497052</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>100</v>
       </c>
@@ -60451,14 +60529,17 @@
       <c r="I13">
         <v>0.1793682638713093</v>
       </c>
-      <c r="J13">
-        <v>0.4598284394497052</v>
+      <c r="J13" t="s">
+        <v>126</v>
       </c>
       <c r="K13">
         <v>0.4598284394497052</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>0.4598284394497052</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>100</v>
       </c>
@@ -60486,14 +60567,17 @@
       <c r="I14">
         <v>0.4146657823352401</v>
       </c>
-      <c r="J14">
-        <v>0.4884415322698737</v>
+      <c r="J14" t="s">
+        <v>127</v>
       </c>
       <c r="K14">
         <v>0.4884415322698737</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>0.4884415322698737</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -60521,14 +60605,17 @@
       <c r="I15">
         <v>0.5821987767652407</v>
       </c>
-      <c r="J15">
-        <v>0.4884415322698737</v>
+      <c r="J15" t="s">
+        <v>128</v>
       </c>
       <c r="K15">
         <v>0.4884415322698737</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>0.4884415322698737</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -60556,14 +60643,17 @@
       <c r="I16">
         <v>0.7271756637212147</v>
       </c>
-      <c r="J16">
-        <v>0.4884415322698737</v>
+      <c r="J16" t="s">
+        <v>126</v>
       </c>
       <c r="K16">
         <v>0.4884415322698737</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>0.4884415322698737</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>100</v>
       </c>
@@ -60591,14 +60681,17 @@
       <c r="I17">
         <v>0.8838150186778819</v>
       </c>
-      <c r="J17">
-        <v>0.638565678370718</v>
+      <c r="J17" t="s">
+        <v>125</v>
       </c>
       <c r="K17">
         <v>0.638565678370718</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>0.638565678370718</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -60626,14 +60719,17 @@
       <c r="I18">
         <v>0.8376325648002086</v>
       </c>
-      <c r="J18">
-        <v>0.7051195775447399</v>
+      <c r="J18" t="s">
+        <v>129</v>
       </c>
       <c r="K18">
         <v>0.7051195775447399</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>0.7051195775447399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>100</v>
       </c>
@@ -60661,14 +60757,17 @@
       <c r="I19">
         <v>0.8777926516765233</v>
       </c>
-      <c r="J19">
-        <v>0.7758910503466243</v>
+      <c r="J19" t="s">
+        <v>124</v>
       </c>
       <c r="K19">
         <v>0.7758910503466243</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>0.7758910503466243</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>100</v>
       </c>
@@ -60696,14 +60795,17 @@
       <c r="I20">
         <v>0.9826449004594185</v>
       </c>
-      <c r="J20">
-        <v>0.9719335174841299</v>
+      <c r="J20" t="s">
+        <v>128</v>
       </c>
       <c r="K20">
         <v>0.9719335174841299</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>0.9719335174841299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -60731,14 +60833,17 @@
       <c r="I21">
         <v>0.9955084956373861</v>
       </c>
-      <c r="J21">
-        <v>0.9719335174841299</v>
+      <c r="J21" t="s">
+        <v>130</v>
       </c>
       <c r="K21">
         <v>0.9719335174841299</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>0.9719335174841299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>101</v>
       </c>
@@ -60766,14 +60871,17 @@
       <c r="I22">
         <v>0.4957753984992435</v>
       </c>
-      <c r="J22">
-        <v>0.9892088186479926</v>
+      <c r="J22" t="s">
+        <v>124</v>
       </c>
       <c r="K22">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>101</v>
       </c>
@@ -60801,14 +60909,17 @@
       <c r="I23">
         <v>0.9793622437756129</v>
       </c>
-      <c r="J23">
-        <v>0.9892088186479926</v>
+      <c r="J23" t="s">
+        <v>122</v>
       </c>
       <c r="K23">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="L23">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -60836,14 +60947,17 @@
       <c r="I24">
         <v>0.7776274591027104</v>
       </c>
-      <c r="J24">
-        <v>0.9892088186479926</v>
+      <c r="J24" t="s">
+        <v>124</v>
       </c>
       <c r="K24">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="L24">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -60871,14 +60985,17 @@
       <c r="I25">
         <v>0.7243756837255892</v>
       </c>
-      <c r="J25">
-        <v>0.9892088186479926</v>
+      <c r="J25" t="s">
+        <v>122</v>
       </c>
       <c r="K25">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -60906,14 +61023,17 @@
       <c r="I26">
         <v>0.8636493868266493</v>
       </c>
-      <c r="J26">
-        <v>0.9892088186479926</v>
+      <c r="J26" t="s">
+        <v>131</v>
       </c>
       <c r="K26">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="L26">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>101</v>
       </c>
@@ -60941,14 +61061,17 @@
       <c r="I27">
         <v>0.8890431160177537</v>
       </c>
-      <c r="J27">
-        <v>0.9892088186479926</v>
+      <c r="J27" t="s">
+        <v>131</v>
       </c>
       <c r="K27">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="L27">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>101</v>
       </c>
@@ -60976,14 +61099,17 @@
       <c r="I28">
         <v>0.9901869251205113</v>
       </c>
-      <c r="J28">
-        <v>0.9892088186479926</v>
+      <c r="J28" t="s">
+        <v>125</v>
       </c>
       <c r="K28">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="L28">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -61011,14 +61137,17 @@
       <c r="I29">
         <v>0.9858226716025433</v>
       </c>
-      <c r="J29">
-        <v>0.9892088186479926</v>
+      <c r="J29" t="s">
+        <v>129</v>
       </c>
       <c r="K29">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="L29">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -61046,14 +61175,17 @@
       <c r="I30">
         <v>0.989835071699116</v>
       </c>
-      <c r="J30">
-        <v>0.9892088186479926</v>
+      <c r="J30" t="s">
+        <v>129</v>
       </c>
       <c r="K30">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="L30">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>101</v>
       </c>
@@ -61081,14 +61213,17 @@
       <c r="I31">
         <v>0.9975190208638891</v>
       </c>
-      <c r="J31">
-        <v>0.9892088186479926</v>
+      <c r="J31" t="s">
+        <v>129</v>
       </c>
       <c r="K31">
         <v>0.9892088186479926</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="L31">
+        <v>0.9892088186479926</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -61116,14 +61251,17 @@
       <c r="I32">
         <v>0.2404957342803514</v>
       </c>
-      <c r="J32">
-        <v>0.1159804250023178</v>
+      <c r="J32" t="s">
+        <v>128</v>
       </c>
       <c r="K32">
         <v>0.1159804250023178</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="L32">
+        <v>0.1159804250023178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>101</v>
       </c>
@@ -61151,14 +61289,17 @@
       <c r="I33">
         <v>0.2989324022873174</v>
       </c>
-      <c r="J33">
-        <v>0.4951337342560849</v>
+      <c r="J33" t="s">
+        <v>126</v>
       </c>
       <c r="K33">
         <v>0.4951337342560849</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="L33">
+        <v>0.4951337342560849</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -61186,14 +61327,17 @@
       <c r="I34">
         <v>0.4162946958875536</v>
       </c>
-      <c r="J34">
-        <v>0.5539944282969873</v>
+      <c r="J34" t="s">
+        <v>132</v>
       </c>
       <c r="K34">
         <v>0.5539944282969873</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34">
+        <v>0.5539944282969873</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -61221,14 +61365,17 @@
       <c r="I35">
         <v>0.76804879720609</v>
       </c>
-      <c r="J35">
-        <v>0.5539944282969873</v>
+      <c r="J35" t="s">
+        <v>128</v>
       </c>
       <c r="K35">
         <v>0.5539944282969873</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="L35">
+        <v>0.5539944282969873</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>101</v>
       </c>
@@ -61256,14 +61403,17 @@
       <c r="I36">
         <v>0.5969574171580203</v>
       </c>
-      <c r="J36">
-        <v>0.5892917090496032</v>
+      <c r="J36" t="s">
+        <v>128</v>
       </c>
       <c r="K36">
         <v>0.5892917090496032</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="L36">
+        <v>0.5892917090496032</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>101</v>
       </c>
@@ -61291,14 +61441,17 @@
       <c r="I37">
         <v>0.7350406227358874</v>
       </c>
-      <c r="J37">
-        <v>0.6355522727102009</v>
+      <c r="J37" t="s">
+        <v>129</v>
       </c>
       <c r="K37">
         <v>0.6355522727102009</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="L37">
+        <v>0.6355522727102009</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>101</v>
       </c>
@@ -61326,14 +61479,17 @@
       <c r="I38">
         <v>0.873652180817604</v>
       </c>
-      <c r="J38">
-        <v>0.6556704619431973</v>
+      <c r="J38" t="s">
+        <v>132</v>
       </c>
       <c r="K38">
         <v>0.6556704619431973</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="L38">
+        <v>0.6556704619431973</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>101</v>
       </c>
@@ -61361,14 +61517,17 @@
       <c r="I39">
         <v>0.9927311732546494</v>
       </c>
-      <c r="J39">
-        <v>0.8532714675548421</v>
+      <c r="J39" t="s">
+        <v>126</v>
       </c>
       <c r="K39">
         <v>0.8532714675548421</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="L39">
+        <v>0.8532714675548421</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -61396,14 +61555,17 @@
       <c r="I40">
         <v>0.9935237318190135</v>
       </c>
-      <c r="J40">
-        <v>0.9363822740072988</v>
+      <c r="J40" t="s">
+        <v>133</v>
       </c>
       <c r="K40">
         <v>0.9363822740072988</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="L40">
+        <v>0.9363822740072988</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -61431,14 +61593,17 @@
       <c r="I41">
         <v>0.9932376932112184</v>
       </c>
-      <c r="J41">
-        <v>0.9980972084393301</v>
+      <c r="J41" t="s">
+        <v>134</v>
       </c>
       <c r="K41">
         <v>0.9980972084393301</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="L41">
+        <v>0.9980972084393301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>104</v>
       </c>
@@ -61466,14 +61631,17 @@
       <c r="I42">
         <v>0.5758860248537963</v>
       </c>
-      <c r="J42">
-        <v>0.5968174531961333</v>
+      <c r="J42" t="s">
+        <v>124</v>
       </c>
       <c r="K42">
         <v>0.5968174531961333</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="L42">
+        <v>0.5968174531961333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>104</v>
       </c>
@@ -61501,14 +61669,17 @@
       <c r="I43">
         <v>0.8586206864531141</v>
       </c>
-      <c r="J43">
-        <v>0.5968174531961333</v>
+      <c r="J43" t="s">
+        <v>124</v>
       </c>
       <c r="K43">
         <v>0.5968174531961333</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="L43">
+        <v>0.5968174531961333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>104</v>
       </c>
@@ -61536,14 +61707,17 @@
       <c r="I44">
         <v>0.8581967169625183</v>
       </c>
-      <c r="J44">
-        <v>0.5968174531961333</v>
+      <c r="J44" t="s">
+        <v>122</v>
       </c>
       <c r="K44">
         <v>0.5968174531961333</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="L44">
+        <v>0.5968174531961333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>104</v>
       </c>
@@ -61571,14 +61745,17 @@
       <c r="I45">
         <v>0.7575513079260172</v>
       </c>
-      <c r="J45">
-        <v>0.5968174531961333</v>
+      <c r="J45" t="s">
+        <v>124</v>
       </c>
       <c r="K45">
         <v>0.5968174531961333</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="L45">
+        <v>0.5968174531961333</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>104</v>
       </c>
@@ -61606,14 +61783,17 @@
       <c r="I46">
         <v>0.7377472293495856</v>
       </c>
-      <c r="J46">
-        <v>0.5968174531961333</v>
+      <c r="J46" t="s">
+        <v>124</v>
       </c>
       <c r="K46">
         <v>0.5968174531961333</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="L46">
+        <v>0.5968174531961333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>104</v>
       </c>
@@ -61641,14 +61821,17 @@
       <c r="I47">
         <v>0.8069151525749726</v>
       </c>
-      <c r="J47">
-        <v>0.7182607447878208</v>
+      <c r="J47" t="s">
+        <v>123</v>
       </c>
       <c r="K47">
         <v>0.7182607447878208</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="L47">
+        <v>0.7182607447878208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -61676,14 +61859,17 @@
       <c r="I48">
         <v>0.9543843063677738</v>
       </c>
-      <c r="J48">
-        <v>0.7182607447878208</v>
+      <c r="J48" t="s">
+        <v>126</v>
       </c>
       <c r="K48">
         <v>0.7182607447878208</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="L48">
+        <v>0.7182607447878208</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -61711,14 +61897,17 @@
       <c r="I49">
         <v>0.8005667150296671</v>
       </c>
-      <c r="J49">
-        <v>0.7182607447878208</v>
+      <c r="J49" t="s">
+        <v>125</v>
       </c>
       <c r="K49">
         <v>0.7182607447878208</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="L49">
+        <v>0.7182607447878208</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>104</v>
       </c>
@@ -61746,14 +61935,17 @@
       <c r="I50">
         <v>0.8255735999434984</v>
       </c>
-      <c r="J50">
-        <v>0.7182607447878208</v>
+      <c r="J50" t="s">
+        <v>129</v>
       </c>
       <c r="K50">
         <v>0.7182607447878208</v>
       </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="L50">
+        <v>0.7182607447878208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -61781,14 +61973,17 @@
       <c r="I51">
         <v>0.9374581634971568</v>
       </c>
-      <c r="J51">
-        <v>0.7462947348118398</v>
+      <c r="J51" t="s">
+        <v>125</v>
       </c>
       <c r="K51">
         <v>0.7462947348118398</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="L51">
+        <v>0.7462947348118398</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -61816,14 +62011,17 @@
       <c r="I52">
         <v>0.005019482580701637</v>
       </c>
-      <c r="J52">
-        <v>0.00454832221004897</v>
+      <c r="J52" t="s">
+        <v>128</v>
       </c>
       <c r="K52">
         <v>0.00454832221004897</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="L52">
+        <v>0.00454832221004897</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -61851,14 +62049,17 @@
       <c r="I53">
         <v>0.2587603084866803</v>
       </c>
-      <c r="J53">
-        <v>0.311821175745764</v>
+      <c r="J53" t="s">
+        <v>126</v>
       </c>
       <c r="K53">
         <v>0.311821175745764</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="L53">
+        <v>0.311821175745764</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -61886,14 +62087,17 @@
       <c r="I54">
         <v>0.5686885600840772</v>
       </c>
-      <c r="J54">
-        <v>0.5190574760136706</v>
+      <c r="J54" t="s">
+        <v>126</v>
       </c>
       <c r="K54">
         <v>0.5190574760136706</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
+      <c r="L54">
+        <v>0.5190574760136706</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -61921,14 +62125,17 @@
       <c r="I55">
         <v>0.4583449925023798</v>
       </c>
-      <c r="J55">
-        <v>0.7430231179889729</v>
+      <c r="J55" t="s">
+        <v>128</v>
       </c>
       <c r="K55">
         <v>0.7430231179889729</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
+      <c r="L55">
+        <v>0.7430231179889729</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>104</v>
       </c>
@@ -61956,14 +62163,17 @@
       <c r="I56">
         <v>0.7303026772403536</v>
       </c>
-      <c r="J56">
-        <v>0.7873436766107218</v>
+      <c r="J56" t="s">
+        <v>125</v>
       </c>
       <c r="K56">
         <v>0.7873436766107218</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="L56">
+        <v>0.7873436766107218</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -61991,14 +62201,17 @@
       <c r="I57">
         <v>0.939043716594085</v>
       </c>
-      <c r="J57">
-        <v>0.7893561473741519</v>
+      <c r="J57" t="s">
+        <v>124</v>
       </c>
       <c r="K57">
         <v>0.7893561473741519</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="L57">
+        <v>0.7893561473741519</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>104</v>
       </c>
@@ -62026,14 +62239,17 @@
       <c r="I58">
         <v>0.9790977168929719</v>
       </c>
-      <c r="J58">
-        <v>0.7893561473741519</v>
+      <c r="J58" t="s">
+        <v>129</v>
       </c>
       <c r="K58">
         <v>0.7893561473741519</v>
       </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="L58">
+        <v>0.7893561473741519</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>104</v>
       </c>
@@ -62061,14 +62277,17 @@
       <c r="I59">
         <v>0.988416738018894</v>
       </c>
-      <c r="J59">
-        <v>0.7893561473741519</v>
+      <c r="J59" t="s">
+        <v>124</v>
       </c>
       <c r="K59">
         <v>0.7893561473741519</v>
       </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="L59">
+        <v>0.7893561473741519</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -62096,14 +62315,17 @@
       <c r="I60">
         <v>0.9157519224732398</v>
       </c>
-      <c r="J60">
-        <v>0.8674561152643865</v>
+      <c r="J60" t="s">
+        <v>124</v>
       </c>
       <c r="K60">
         <v>0.8674561152643865</v>
       </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="L60">
+        <v>0.8674561152643865</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>104</v>
       </c>
@@ -62131,10 +62353,13 @@
       <c r="I61">
         <v>0.9806299539390264</v>
       </c>
-      <c r="J61">
+      <c r="J61" t="s">
+        <v>129</v>
+      </c>
+      <c r="K61">
         <v>0.8674561152643865</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>0.8674561152643865</v>
       </c>
     </row>
